--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/08,26/31,08,26 Останкино КИ и ЗПФ/машина САП 06,09 Донецк_КарловаБаранова_Малахутин_ПРС КИ/Заказ ЛП_Малахутин 06.09.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/08,26/31,08,26 Останкино КИ и ЗПФ/машина САП 06,09 Донецк_КарловаБаранова_Малахутин_ПРС КИ/Заказ ЛП_Малахутин 06.09.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ и ЗПФ\02,09 Малахутин\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\08,26\31,08,26 Останкино КИ и ЗПФ\машина САП 06,09 Донецк_КарловаБаранова_Малахутин_ПРС КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27B25B54-E9A7-4E46-98A5-F8C5FEA9BA8E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0C87268-8EC0-4200-A354-E55E1C9DC51D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6259,7 +6259,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:BO1692"/>
@@ -6482,7 +6482,7 @@
       <c r="BN9" s="120"/>
       <c r="BO9" s="120"/>
     </row>
-    <row r="10" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:67" ht="16.5" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="48"/>
       <c r="B10" s="43" t="s">
         <v>18</v>
@@ -6496,7 +6496,7 @@
       <c r="I10" s="43"/>
       <c r="J10" s="44"/>
     </row>
-    <row r="11" spans="1:67" s="15" customFormat="1" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:67" s="15" customFormat="1" ht="16.5" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A11" s="58">
         <v>4561</v>
       </c>
@@ -6582,7 +6582,7 @@
       <c r="BN11" s="121"/>
       <c r="BO11" s="121"/>
     </row>
-    <row r="12" spans="1:67" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:67" s="15" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="145">
         <v>7536</v>
       </c>
@@ -6670,7 +6670,7 @@
       <c r="BN12" s="121"/>
       <c r="BO12" s="121"/>
     </row>
-    <row r="13" spans="1:67" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:67" s="15" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="58">
         <v>5851</v>
       </c>
@@ -6756,7 +6756,7 @@
       <c r="BN13" s="121"/>
       <c r="BO13" s="121"/>
     </row>
-    <row r="14" spans="1:67" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:67" s="15" customFormat="1" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A14" s="58">
         <v>4813</v>
       </c>
@@ -6844,7 +6844,7 @@
       <c r="BN14" s="121"/>
       <c r="BO14" s="121"/>
     </row>
-    <row r="15" spans="1:67" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:67" s="15" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="58">
         <v>4574</v>
       </c>
@@ -7064,7 +7064,7 @@
       <c r="J18" s="29"/>
       <c r="L18" s="122"/>
     </row>
-    <row r="19" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="58">
         <v>6861</v>
       </c>
@@ -7094,7 +7094,7 @@
       <c r="J19" s="29"/>
       <c r="L19" s="122"/>
     </row>
-    <row r="20" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="58">
         <v>6862</v>
       </c>
@@ -7124,7 +7124,7 @@
       <c r="J20" s="29"/>
       <c r="L20" s="122"/>
     </row>
-    <row r="21" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="145">
         <v>7539</v>
       </c>
@@ -7156,7 +7156,7 @@
       </c>
       <c r="L21" s="122"/>
     </row>
-    <row r="22" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="58">
         <v>7334</v>
       </c>
@@ -7218,7 +7218,7 @@
       <c r="J23" s="29"/>
       <c r="L23" s="122"/>
     </row>
-    <row r="24" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="58">
         <v>8014</v>
       </c>
@@ -7484,7 +7484,7 @@
       <c r="BN26" s="122"/>
       <c r="BO26" s="122"/>
     </row>
-    <row r="27" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="147">
         <v>6340</v>
       </c>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="L27" s="122"/>
     </row>
-    <row r="28" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="147">
         <v>6341</v>
       </c>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="L28" s="122"/>
     </row>
-    <row r="29" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="58">
         <v>6333</v>
       </c>
@@ -7610,7 +7610,7 @@
       <c r="J30" s="61"/>
       <c r="L30" s="122"/>
     </row>
-    <row r="31" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="58">
         <v>7343</v>
       </c>
@@ -7728,7 +7728,7 @@
       <c r="BN32" s="122"/>
       <c r="BO32" s="122"/>
     </row>
-    <row r="33" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A33" s="58">
         <v>7231</v>
       </c>
@@ -7814,7 +7814,7 @@
       <c r="BN33" s="122"/>
       <c r="BO33" s="122"/>
     </row>
-    <row r="34" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:67" ht="16.5" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="48" t="s">
         <v>104</v>
       </c>
@@ -7831,7 +7831,7 @@
       <c r="J34" s="44"/>
       <c r="L34" s="122"/>
     </row>
-    <row r="35" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A35" s="58">
         <v>6767</v>
       </c>
@@ -7917,7 +7917,7 @@
       <c r="BN35" s="122"/>
       <c r="BO35" s="122"/>
     </row>
-    <row r="36" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="58">
         <v>6761</v>
       </c>
@@ -8003,7 +8003,7 @@
       <c r="BN36" s="122"/>
       <c r="BO36" s="122"/>
     </row>
-    <row r="37" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="58">
         <v>6764</v>
       </c>
@@ -8089,7 +8089,7 @@
       <c r="BN37" s="122"/>
       <c r="BO37" s="122"/>
     </row>
-    <row r="38" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="58">
         <v>6254</v>
       </c>
@@ -8175,7 +8175,7 @@
       <c r="BN38" s="122"/>
       <c r="BO38" s="122"/>
     </row>
-    <row r="39" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="58">
         <v>7075</v>
       </c>
@@ -8525,7 +8525,7 @@
       <c r="BN42" s="122"/>
       <c r="BO42" s="122"/>
     </row>
-    <row r="43" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="58">
         <v>7076</v>
       </c>
@@ -8875,7 +8875,7 @@
       <c r="BN46" s="122"/>
       <c r="BO46" s="122"/>
     </row>
-    <row r="47" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="58">
         <v>6759</v>
       </c>
@@ -9049,7 +9049,7 @@
       <c r="BN48" s="122"/>
       <c r="BO48" s="122"/>
     </row>
-    <row r="49" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="58">
         <v>6765</v>
       </c>
@@ -9135,7 +9135,7 @@
       <c r="BN49" s="122"/>
       <c r="BO49" s="122"/>
     </row>
-    <row r="50" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="58">
         <v>7074</v>
       </c>
@@ -9221,7 +9221,7 @@
       <c r="BN50" s="122"/>
       <c r="BO50" s="122"/>
     </row>
-    <row r="51" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="58">
         <v>7123</v>
       </c>
@@ -9307,7 +9307,7 @@
       <c r="BN51" s="122"/>
       <c r="BO51" s="122"/>
     </row>
-    <row r="52" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="58">
         <v>5819</v>
       </c>
@@ -9393,7 +9393,7 @@
       <c r="BN52" s="122"/>
       <c r="BO52" s="122"/>
     </row>
-    <row r="53" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="58">
         <v>6475</v>
       </c>
@@ -9479,7 +9479,7 @@
       <c r="BN53" s="122"/>
       <c r="BO53" s="122"/>
     </row>
-    <row r="54" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="147">
         <v>7284</v>
       </c>
@@ -9657,7 +9657,7 @@
       <c r="BN55" s="122"/>
       <c r="BO55" s="122"/>
     </row>
-    <row r="56" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="58">
         <v>7601</v>
       </c>
@@ -9743,7 +9743,7 @@
       <c r="BN56" s="122"/>
       <c r="BO56" s="122"/>
     </row>
-    <row r="57" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="147">
         <v>7371</v>
       </c>
@@ -9831,7 +9831,7 @@
       <c r="BN57" s="122"/>
       <c r="BO57" s="122"/>
     </row>
-    <row r="58" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="58">
         <v>6837</v>
       </c>
@@ -9917,7 +9917,7 @@
       <c r="BN58" s="122"/>
       <c r="BO58" s="122"/>
     </row>
-    <row r="59" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="58">
         <v>7080</v>
       </c>
@@ -9947,7 +9947,7 @@
       <c r="J59" s="29"/>
       <c r="L59" s="122"/>
     </row>
-    <row r="60" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="58">
         <v>6724</v>
       </c>
@@ -9977,7 +9977,7 @@
       <c r="J60" s="29"/>
       <c r="L60" s="122"/>
     </row>
-    <row r="61" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="58">
         <v>7066</v>
       </c>
@@ -10007,7 +10007,7 @@
       <c r="J61" s="29"/>
       <c r="L61" s="122"/>
     </row>
-    <row r="62" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="58">
         <v>6713</v>
       </c>
@@ -10069,7 +10069,7 @@
       <c r="J63" s="29"/>
       <c r="L63" s="122"/>
     </row>
-    <row r="64" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="58">
         <v>6602</v>
       </c>
@@ -10099,7 +10099,7 @@
       <c r="J64" s="29"/>
       <c r="L64" s="122"/>
     </row>
-    <row r="65" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="145">
         <v>7040</v>
       </c>
@@ -10131,7 +10131,7 @@
       </c>
       <c r="L65" s="122"/>
     </row>
-    <row r="66" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="145">
         <v>7521</v>
       </c>
@@ -10163,7 +10163,7 @@
       </c>
       <c r="L66" s="122"/>
     </row>
-    <row r="67" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="58">
         <v>7073</v>
       </c>
@@ -10193,7 +10193,7 @@
       <c r="J67" s="29"/>
       <c r="L67" s="122"/>
     </row>
-    <row r="68" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="58">
         <v>7276</v>
       </c>
@@ -10223,7 +10223,7 @@
       <c r="J68" s="29"/>
       <c r="L68" s="122"/>
     </row>
-    <row r="69" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="58">
         <v>6616</v>
       </c>
@@ -10253,7 +10253,7 @@
       <c r="J69" s="29"/>
       <c r="L69" s="122"/>
     </row>
-    <row r="70" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="58">
         <v>7044</v>
       </c>
@@ -10283,7 +10283,7 @@
       <c r="J70" s="29"/>
       <c r="L70" s="122"/>
     </row>
-    <row r="71" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="147">
         <v>7385</v>
       </c>
@@ -10315,7 +10315,7 @@
       </c>
       <c r="L71" s="122"/>
     </row>
-    <row r="72" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12" ht="16.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A72" s="147">
         <v>7460</v>
       </c>
@@ -10347,7 +10347,7 @@
       </c>
       <c r="L72" s="122"/>
     </row>
-    <row r="73" spans="1:12" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:12" ht="16.5" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="48" t="s">
         <v>104</v>
       </c>
@@ -10364,7 +10364,7 @@
       <c r="J73" s="44"/>
       <c r="L73" s="122"/>
     </row>
-    <row r="74" spans="1:12" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12" ht="16.5" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A74" s="58">
         <v>6527</v>
       </c>
@@ -10394,7 +10394,7 @@
       <c r="J74" s="61"/>
       <c r="L74" s="122"/>
     </row>
-    <row r="75" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="58">
         <v>6550</v>
       </c>
@@ -10456,7 +10456,7 @@
       <c r="J76" s="29"/>
       <c r="L76" s="122"/>
     </row>
-    <row r="77" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="58">
         <v>7001</v>
       </c>
@@ -10518,7 +10518,7 @@
       <c r="J78" s="29"/>
       <c r="L78" s="122"/>
     </row>
-    <row r="79" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="58">
         <v>7059</v>
       </c>
@@ -10548,7 +10548,7 @@
       <c r="J79" s="29"/>
       <c r="L79" s="122"/>
     </row>
-    <row r="80" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="58">
         <v>6609</v>
       </c>
@@ -10580,7 +10580,7 @@
       <c r="J80" s="29"/>
       <c r="L80" s="122"/>
     </row>
-    <row r="81" spans="1:12" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:12" ht="16.5" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="48" t="s">
         <v>104</v>
       </c>
@@ -10597,7 +10597,7 @@
       <c r="J81" s="44"/>
       <c r="L81" s="122"/>
     </row>
-    <row r="82" spans="1:12" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:12" ht="16.5" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A82" s="145">
         <v>7564</v>
       </c>
@@ -10629,7 +10629,7 @@
       </c>
       <c r="L82" s="122"/>
     </row>
-    <row r="83" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="58">
         <v>7133</v>
       </c>
@@ -10659,7 +10659,7 @@
       <c r="J83" s="61"/>
       <c r="L83" s="122"/>
     </row>
-    <row r="84" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="58">
         <v>6946</v>
       </c>
@@ -10689,7 +10689,7 @@
       <c r="J84" s="29"/>
       <c r="L84" s="122"/>
     </row>
-    <row r="85" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="58">
         <v>7132</v>
       </c>
@@ -10881,7 +10881,7 @@
       </c>
       <c r="L90" s="122"/>
     </row>
-    <row r="91" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="145">
         <v>7489</v>
       </c>
@@ -10913,7 +10913,7 @@
       </c>
       <c r="L91" s="122"/>
     </row>
-    <row r="92" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="58">
         <v>6807</v>
       </c>
@@ -10943,7 +10943,7 @@
       <c r="J92" s="29"/>
       <c r="L92" s="122"/>
     </row>
-    <row r="93" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="58">
         <v>6787</v>
       </c>
@@ -11037,7 +11037,7 @@
       <c r="J95" s="29"/>
       <c r="L95" s="122"/>
     </row>
-    <row r="96" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:12" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="58">
         <v>7233</v>
       </c>
@@ -11099,7 +11099,7 @@
       <c r="J97" s="50"/>
       <c r="L97" s="122"/>
     </row>
-    <row r="98" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:67" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="58">
         <v>7177</v>
       </c>
@@ -11193,7 +11193,7 @@
       <c r="J100" s="50"/>
       <c r="L100" s="122"/>
     </row>
-    <row r="101" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:67" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="58">
         <v>7238</v>
       </c>
@@ -11223,7 +11223,7 @@
       <c r="J101" s="50"/>
       <c r="L101" s="122"/>
     </row>
-    <row r="102" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:67" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="147">
         <v>7237</v>
       </c>
@@ -11255,7 +11255,7 @@
       </c>
       <c r="L102" s="122"/>
     </row>
-    <row r="103" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:67" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="58">
         <v>7241</v>
       </c>
@@ -11285,7 +11285,7 @@
       <c r="J103" s="50"/>
       <c r="L103" s="122"/>
     </row>
-    <row r="104" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:67" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="58">
         <v>7332</v>
       </c>
@@ -11315,7 +11315,7 @@
       <c r="J104" s="50"/>
       <c r="L104" s="122"/>
     </row>
-    <row r="105" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:67" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="58">
         <v>7333</v>
       </c>
@@ -11345,7 +11345,7 @@
       <c r="J105" s="50"/>
       <c r="L105" s="122"/>
     </row>
-    <row r="106" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:67" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="145">
         <v>7608</v>
       </c>
@@ -11377,7 +11377,7 @@
       </c>
       <c r="L106" s="122"/>
     </row>
-    <row r="107" spans="1:67" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:67" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A107" s="145">
         <v>7610</v>
       </c>
@@ -11409,7 +11409,7 @@
       </c>
       <c r="L107" s="122"/>
     </row>
-    <row r="108" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="48" t="s">
         <v>104</v>
       </c>
@@ -11482,7 +11482,7 @@
       <c r="BN108" s="122"/>
       <c r="BO108" s="122"/>
     </row>
-    <row r="109" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A109" s="58">
         <v>614</v>
       </c>
@@ -11568,7 +11568,7 @@
       <c r="BN109" s="122"/>
       <c r="BO109" s="122"/>
     </row>
-    <row r="110" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="58">
         <v>3287</v>
       </c>
@@ -11654,7 +11654,7 @@
       <c r="BN110" s="122"/>
       <c r="BO110" s="122"/>
     </row>
-    <row r="111" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="58">
         <v>5708</v>
       </c>
@@ -11684,7 +11684,7 @@
       <c r="J111" s="29"/>
       <c r="L111" s="122"/>
     </row>
-    <row r="112" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="58">
         <v>4117</v>
       </c>
@@ -11714,7 +11714,7 @@
       <c r="J112" s="29"/>
       <c r="L112" s="122"/>
     </row>
-    <row r="113" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="58">
         <v>7316</v>
       </c>
@@ -11744,7 +11744,7 @@
       <c r="J113" s="29"/>
       <c r="L113" s="122"/>
     </row>
-    <row r="114" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="58">
         <v>7317</v>
       </c>
@@ -11774,7 +11774,7 @@
       <c r="J114" s="29"/>
       <c r="L114" s="122"/>
     </row>
-    <row r="115" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="58">
         <v>7143</v>
       </c>
@@ -11836,7 +11836,7 @@
       <c r="J116" s="29"/>
       <c r="L116" s="122"/>
     </row>
-    <row r="117" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="58">
         <v>7456</v>
       </c>
@@ -11866,7 +11866,7 @@
       <c r="J117" s="29"/>
       <c r="L117" s="122"/>
     </row>
-    <row r="118" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="58">
         <v>7318</v>
       </c>
@@ -11960,7 +11960,7 @@
       <c r="J120" s="29"/>
       <c r="L120" s="122"/>
     </row>
-    <row r="121" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="58">
         <v>7383</v>
       </c>
@@ -12022,7 +12022,7 @@
       <c r="J122" s="29"/>
       <c r="L122" s="122"/>
     </row>
-    <row r="123" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="58">
         <v>4993</v>
       </c>
@@ -12116,7 +12116,7 @@
       <c r="J125" s="29"/>
       <c r="L125" s="122"/>
     </row>
-    <row r="126" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="58">
         <v>5931</v>
       </c>
@@ -12146,7 +12146,7 @@
       <c r="J126" s="29"/>
       <c r="L126" s="122"/>
     </row>
-    <row r="127" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="58">
         <v>6832</v>
       </c>
@@ -12176,7 +12176,7 @@
       <c r="J127" s="29"/>
       <c r="L127" s="122"/>
     </row>
-    <row r="128" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="58">
         <v>7299</v>
       </c>
@@ -12206,7 +12206,7 @@
       <c r="J128" s="29"/>
       <c r="L128" s="122"/>
     </row>
-    <row r="129" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="58">
         <v>7386</v>
       </c>
@@ -12236,7 +12236,7 @@
       <c r="J129" s="29"/>
       <c r="L129" s="122"/>
     </row>
-    <row r="130" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="58">
         <v>5679</v>
       </c>
@@ -12398,7 +12398,7 @@
       <c r="J134" s="29"/>
       <c r="L134" s="122"/>
     </row>
-    <row r="135" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="58">
         <v>6222</v>
       </c>
@@ -12428,7 +12428,7 @@
       <c r="J135" s="29"/>
       <c r="L135" s="122"/>
     </row>
-    <row r="136" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="147">
         <v>6834</v>
       </c>
@@ -12460,7 +12460,7 @@
       </c>
       <c r="L136" s="122"/>
     </row>
-    <row r="137" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="147">
         <v>6965</v>
       </c>
@@ -12492,7 +12492,7 @@
       </c>
       <c r="L137" s="122"/>
     </row>
-    <row r="138" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="147">
         <v>6557</v>
       </c>
@@ -12524,7 +12524,7 @@
       </c>
       <c r="L138" s="122"/>
     </row>
-    <row r="139" spans="1:67" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="145">
         <v>7626</v>
       </c>
@@ -12558,7 +12558,7 @@
       </c>
       <c r="L139" s="122"/>
     </row>
-    <row r="140" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:67" ht="16.5" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A140" s="48" t="s">
         <v>104</v>
       </c>
@@ -12575,7 +12575,7 @@
       <c r="J140" s="44"/>
       <c r="L140" s="122"/>
     </row>
-    <row r="141" spans="1:67" ht="16.149999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:67" ht="16.149999999999999" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A141" s="58">
         <v>6470</v>
       </c>
@@ -12605,7 +12605,7 @@
       <c r="J141" s="29"/>
       <c r="L141" s="122"/>
     </row>
-    <row r="142" spans="1:67" s="63" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:67" s="63" customFormat="1" ht="16.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="58">
         <v>6495</v>
       </c>
@@ -12691,7 +12691,7 @@
       <c r="BN142" s="122"/>
       <c r="BO142" s="122"/>
     </row>
-    <row r="143" spans="1:67" s="63" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:67" s="63" customFormat="1" ht="16.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="58">
         <v>5452</v>
       </c>
@@ -12777,7 +12777,7 @@
       <c r="BN143" s="122"/>
       <c r="BO143" s="122"/>
     </row>
-    <row r="144" spans="1:67" s="63" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:67" s="63" customFormat="1" ht="16.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="58">
         <v>6866</v>
       </c>
@@ -12863,7 +12863,7 @@
       <c r="BN144" s="122"/>
       <c r="BO144" s="122"/>
     </row>
-    <row r="145" spans="1:67" s="63" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:67" s="63" customFormat="1" ht="16.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="58">
         <v>6025</v>
       </c>
@@ -12949,7 +12949,7 @@
       <c r="BN145" s="122"/>
       <c r="BO145" s="122"/>
     </row>
-    <row r="146" spans="1:67" s="63" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:67" s="63" customFormat="1" ht="16.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="58">
         <v>4584</v>
       </c>
@@ -13211,7 +13211,7 @@
       <c r="BN148" s="122"/>
       <c r="BO148" s="122"/>
     </row>
-    <row r="149" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="58">
         <v>7377</v>
       </c>
@@ -13297,7 +13297,7 @@
       <c r="BN149" s="122"/>
       <c r="BO149" s="122"/>
     </row>
-    <row r="150" spans="1:67" s="63" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:67" s="63" customFormat="1" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="58">
         <v>6925</v>
       </c>
@@ -13383,7 +13383,7 @@
       <c r="BN150" s="122"/>
       <c r="BO150" s="122"/>
     </row>
-    <row r="151" spans="1:67" s="63" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:67" s="63" customFormat="1" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="145">
         <v>7647</v>
       </c>
@@ -13471,7 +13471,7 @@
       <c r="BN151" s="122"/>
       <c r="BO151" s="122"/>
     </row>
-    <row r="152" spans="1:67" s="63" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:67" s="63" customFormat="1" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A152" s="145">
         <v>7651</v>
       </c>
@@ -13559,7 +13559,7 @@
       <c r="BN152" s="122"/>
       <c r="BO152" s="122"/>
     </row>
-    <row r="153" spans="1:67" s="63" customFormat="1" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:67" s="63" customFormat="1" ht="15.75" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A153" s="48" t="s">
         <v>104</v>
       </c>
@@ -13632,7 +13632,7 @@
       <c r="BN153" s="122"/>
       <c r="BO153" s="122"/>
     </row>
-    <row r="154" spans="1:67" s="63" customFormat="1" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:67" s="63" customFormat="1" ht="15.75" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A154" s="145">
         <v>7485</v>
       </c>
@@ -13720,7 +13720,7 @@
       <c r="BN154" s="122"/>
       <c r="BO154" s="122"/>
     </row>
-    <row r="155" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:67" ht="16.5" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A155" s="48" t="s">
         <v>104</v>
       </c>
@@ -13737,7 +13737,7 @@
       <c r="J155" s="44"/>
       <c r="L155" s="122"/>
     </row>
-    <row r="156" spans="1:67" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:67" ht="16.5" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A156" s="58">
         <v>6620</v>
       </c>
@@ -13799,7 +13799,7 @@
       <c r="J157" s="29"/>
       <c r="L157" s="122"/>
     </row>
-    <row r="158" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="145">
         <v>6008</v>
       </c>
@@ -13927,7 +13927,7 @@
       <c r="J161" s="29"/>
       <c r="L161" s="122"/>
     </row>
-    <row r="162" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="58">
         <v>7092</v>
       </c>
@@ -13957,7 +13957,7 @@
       <c r="J162" s="29"/>
       <c r="L162" s="122"/>
     </row>
-    <row r="163" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="58">
         <v>6448</v>
       </c>
@@ -14019,7 +14019,7 @@
       <c r="J164" s="29"/>
       <c r="L164" s="122"/>
     </row>
-    <row r="165" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="58">
         <v>6208</v>
       </c>
@@ -14049,7 +14049,7 @@
       <c r="J165" s="29"/>
       <c r="L165" s="122"/>
     </row>
-    <row r="166" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="58">
         <v>6228</v>
       </c>
@@ -29377,7 +29377,13 @@
       <c r="J1692" s="21"/>
     </row>
   </sheetData>
-  <autoFilter ref="A9:J168" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A9:J168" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <filterColumn colId="4">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="2">
     <mergeCell ref="E1:J1"/>
     <mergeCell ref="G3:J3"/>
